--- a/artfynd/A 19141-2026 artfynd.xlsx
+++ b/artfynd/A 19141-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567818</v>
+        <v>81760630</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fallviken-Grönviken, Gstr</t>
+          <t>Åmot, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572650</v>
+        <v>572295</v>
       </c>
       <c r="R2" t="n">
-        <v>6764772</v>
+        <v>6764879</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,34 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114571628</v>
+        <v>81760935</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fallviken-Grönviken, Gstr</t>
+          <t>Åmot, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572903</v>
+        <v>572257</v>
       </c>
       <c r="R3" t="n">
-        <v>6764788</v>
+        <v>6764919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,73 +861,63 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114567823</v>
+        <v>81760491</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fallviken-Grönviken, Gstr</t>
+          <t>Åmot, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572908</v>
+        <v>572253</v>
       </c>
       <c r="R4" t="n">
-        <v>6764804</v>
+        <v>6764924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,34 +963,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Axel Linder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist</t>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114567820</v>
+        <v>114567818</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,11 +1009,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1043,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572686</v>
+        <v>572650</v>
       </c>
       <c r="R5" t="n">
-        <v>6764851</v>
+        <v>6764772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,6 +1080,741 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114567820</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572686</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6764851</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114571628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572903</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6764788</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81760629</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åmot, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572930</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6764763</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114564876</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572738</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6765000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114564875</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572737</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6764999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81760490</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åmot, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572933</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6764767</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Ecocom AB</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Axel Linder</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114567823</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fallviken-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572908</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6764804</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
